--- a/sources/julia_step2.xlsx
+++ b/sources/julia_step2.xlsx
@@ -422,7 +422,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3149,7 +3149,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
